--- a/simulations/scene/inputs/Scenarios_25_12_11.xlsx
+++ b/simulations/scene/inputs/Scenarios_25_12_11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp06503\work_home\tigerault\Wheat-BRIDGES_framework\Root-CyNAPS\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFF8CBB-423D-4CAB-BE66-218CF13997EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA420318-0B39-4F0F-BE53-EF536C50FF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="105" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="285">
   <si>
     <t>input_file</t>
   </si>
@@ -879,10 +879,16 @@
     <t>diffusion_xylem_AA_P</t>
   </si>
   <si>
-    <t>fixed_collar_axial_diffusivity</t>
-  </si>
-  <si>
     <t>Option to enforce the axial diffusivity of solutes in phloem at the shoot-root junction</t>
+  </si>
+  <si>
+    <t>mass_wise_phloem_wiring</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>False</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1440,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1473,6 +1479,9 @@
     </xf>
     <xf numFmtId="11" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -3928,7 +3937,7 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>177</v>
@@ -3940,67 +3949,67 @@
         <v>209</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="I32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="J32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="K32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="L32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="M32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="N32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="O32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="P32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="Q32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="R32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="S32" s="10">
-        <v>8.0000000000000005E-9</v>
-      </c>
-      <c r="T32" s="10">
-        <v>8.0000000000000005E-9</v>
+      <c r="G32" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="P32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="R32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="S32" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="T32" s="10" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G29:G30">
+    <cfRule type="colorScale" priority="629">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="628">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="629">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4034,17 +4043,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H17">
+    <cfRule type="colorScale" priority="128">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="127">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="128">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4166,17 +4175,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:T11">
+    <cfRule type="colorScale" priority="744">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="743">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="744">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4188,6 +4197,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:T13">
+    <cfRule type="colorScale" priority="746">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="745">
       <colorScale>
         <cfvo type="min"/>
@@ -4198,7 +4217,151 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="746">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14:T14">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:T15">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18:T18">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19:T19">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20:T20">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:T21">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:T22">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4231,6 +4394,50 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H27:T27">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H28:T28">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H29:T30">
     <cfRule type="colorScale" priority="728">
       <colorScale>
@@ -4253,7 +4460,101 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="H31:T31">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32:T32">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="156">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="155">
       <colorScale>
         <cfvo type="min"/>
@@ -4264,7 +4565,41 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="156">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16:T16">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17:T17">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4320,17 +4655,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3">
+    <cfRule type="colorScale" priority="150">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="149">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4430,17 +4765,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3">
+    <cfRule type="colorScale" priority="140">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="139">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="140">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4452,17 +4787,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R3">
+    <cfRule type="colorScale" priority="138">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="137">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="138">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4507,336 +4842,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="132">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:T14">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:T15">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16:T16">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17:T17">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19:T19">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18:T18">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20:T20">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H21:T21">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H22:T22">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H27:T27">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28:T28">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31:T31">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31:T31">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:T32">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32:T32">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/scene/inputs/Scenarios_25_12_11.xlsx
+++ b/simulations/scene/inputs/Scenarios_25_12_11.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp06503\work_home\tigerault\Wheat-BRIDGES_framework\Root-CyNAPS\simulations\scene\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp54510\work_home\tigerault\Wheat-BRIDGES_framework\Root-CyNAPS\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA420318-0B39-4F0F-BE53-EF536C50FF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1762FF8-D615-4F88-A1F7-2E488AC900AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="105" windowWidth="25440" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="298">
   <si>
     <t>input_file</t>
   </si>
@@ -889,6 +892,45 @@
   </si>
   <si>
     <t>False</t>
+  </si>
+  <si>
+    <t>reference_rate_of_AA_consumption_by_growth</t>
+  </si>
+  <si>
+    <t>Reference rate of amino acids for growth (used to proportionnally increase the permeability of phloem according to the actual rate of amino_acid consumption)</t>
+  </si>
+  <si>
+    <t>Real number / mol of amino acids per second</t>
+  </si>
+  <si>
+    <t>diffusion_apoplasm</t>
+  </si>
+  <si>
+    <t>Diffusion paramenter for exchanges between xylem apoplasm and soil solution</t>
+  </si>
+  <si>
+    <t>increased_wall_resistance_factor</t>
+  </si>
+  <si>
+    <t>dimensionless</t>
+  </si>
+  <si>
+    <t>stele wall resistance increase factor to avoid overestimation of xylem-phloem conductance</t>
+  </si>
+  <si>
+    <t>max_loading_rate</t>
+  </si>
+  <si>
+    <t>Reference temperature for setting the temperature-dependence of phloem loading</t>
+  </si>
+  <si>
+    <t>Real number / degree Celsius</t>
+  </si>
+  <si>
+    <t>Affinity constant (in terms of Michaelis-Menten formalism) for phloem loading, corresponding to the concentration for which the rate is equal to half of the maximal rate</t>
+  </si>
+  <si>
+    <t>Real number / mol of hexose per gram of root dry structural mass</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1482,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1483,50 +1525,54 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
     <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
     <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Avertissement" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Calcul" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Cellule liée" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Entrée" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Insatisfaisant" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutre" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Satisfaisant" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Sortie" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texte explicatif" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Titre" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Titre 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Titre 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Titre 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Titre 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Vérification" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1804,8 +1850,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
     <col min="2" max="4" width="15" style="1" customWidth="1"/>
@@ -2674,7 +2720,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>177</v>
@@ -2686,145 +2732,132 @@
         <v>209</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="10">
+        <v>1E-14</v>
+      </c>
+      <c r="H14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="I14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="J14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="K14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="L14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="M14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="N14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="O14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="P14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="R14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="S14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+      <c r="T14" s="10">
+        <v>4.9999999999999999E-13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G15" s="15">
         <v>1.2E-8</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H15" s="10">
         <f>0.00000000005 *2</f>
         <v>1E-10</v>
       </c>
-      <c r="I14" s="10">
-        <f t="shared" ref="I14:T14" si="3">0.00000000005 *2</f>
+      <c r="I15" s="10">
+        <f t="shared" ref="I15:T15" si="3">0.00000000005 *2</f>
         <v>1E-10</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="S14" s="10">
+      <c r="S15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
-      <c r="T14" s="10">
+      <c r="T15" s="10">
         <f t="shared" si="3"/>
         <v>1E-10</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1.2E-8</v>
-      </c>
-      <c r="H15" s="10">
-        <f>H14/10/4</f>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="I15" s="10">
-        <f t="shared" ref="I15:T15" si="4">I14/10/4</f>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="J15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="K15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="L15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="M15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="N15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="O15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="P15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="Q15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="R15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="S15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-      <c r="T15" s="10">
-        <f t="shared" si="4"/>
-        <v>2.5000000000000003E-12</v>
-      </c>
-    </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>177</v>
@@ -2839,278 +2872,279 @@
         <v>220</v>
       </c>
       <c r="F16" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G16" s="15">
+        <v>1.2E-8</v>
+      </c>
+      <c r="H16" s="10">
+        <f>H15/10/4</f>
+        <v>2.5000000000000003E-12</v>
+      </c>
+      <c r="I16" s="10">
+        <f>I15</f>
+        <v>1E-10</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" ref="J16:T16" si="4">J15</f>
+        <v>1E-10</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="M16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="O16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="P16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="Q16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="R16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="S16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+      <c r="T16" s="10">
+        <f t="shared" si="4"/>
+        <v>1E-10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G17" s="15">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="H16" s="10">
-        <f t="shared" ref="H16" si="5">0.0000001 * 10 /2 / 100 /2</f>
-        <v>2.5000000000000001E-9</v>
-      </c>
-      <c r="I16" s="10">
+      <c r="H17" s="10">
         <f>0.00000001</f>
         <v>1E-8</v>
       </c>
-      <c r="J16" s="10">
-        <f t="shared" ref="J16:T16" si="6">0.00000001</f>
-        <v>1E-8</v>
-      </c>
-      <c r="K16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="L16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="M16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="N16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="O16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="P16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="Q16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="R16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="S16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-      <c r="T16" s="10">
-        <f t="shared" si="6"/>
-        <v>1E-8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="I17" s="10">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>0</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>0</v>
+      </c>
+      <c r="P17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>0</v>
+      </c>
+      <c r="R17" s="10">
+        <v>0</v>
+      </c>
+      <c r="S17" s="10">
+        <v>0</v>
+      </c>
+      <c r="T17" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E18" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F18" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G18" s="15">
         <v>100</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H18" s="10">
         <v>1000</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="R17" s="10">
+      <c r="R18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="S17" s="10">
+      <c r="S18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
-      <c r="T17" s="10">
+      <c r="T18" s="10">
         <f>100</f>
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F19" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G19" s="15">
         <v>9.9999999999999995E-8</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H19" s="10">
         <f>0.000001 / 10000 / 4 / 10 /5</f>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="I18" s="10">
-        <f t="shared" ref="I18:T18" si="7">0.000001 / 10000 / 4 / 10 /5</f>
+      <c r="I19" s="10">
+        <f t="shared" ref="I19:T19" si="5">0.000001 / 10000 / 4 / 10 /5</f>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="J18" s="10">
-        <f t="shared" si="7"/>
+      <c r="J19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="K18" s="10">
-        <f t="shared" si="7"/>
+      <c r="K19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="L18" s="10">
-        <f t="shared" si="7"/>
+      <c r="L19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="M18" s="10">
-        <f t="shared" si="7"/>
+      <c r="M19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="N18" s="10">
-        <f t="shared" si="7"/>
+      <c r="N19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="O18" s="10">
-        <f t="shared" si="7"/>
+      <c r="O19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="P18" s="10">
-        <f t="shared" si="7"/>
+      <c r="P19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="Q18" s="10">
-        <f t="shared" si="7"/>
+      <c r="Q19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="R18" s="10">
-        <f t="shared" si="7"/>
+      <c r="R19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="S18" s="10">
-        <f t="shared" si="7"/>
+      <c r="S19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
       </c>
-      <c r="T18" s="10">
-        <f t="shared" si="7"/>
+      <c r="T19" s="10">
+        <f t="shared" si="5"/>
         <v>4.9999999999999999E-13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="G19" s="15">
-        <v>9.9999999999999995E-8</v>
-      </c>
-      <c r="H19" s="10">
-        <v>0</v>
-      </c>
-      <c r="I19" s="10">
-        <v>0</v>
-      </c>
-      <c r="J19" s="10">
-        <v>0</v>
-      </c>
-      <c r="K19" s="10">
-        <v>0</v>
-      </c>
-      <c r="L19" s="10">
-        <v>0</v>
-      </c>
-      <c r="M19" s="10">
-        <v>0</v>
-      </c>
-      <c r="N19" s="10">
-        <v>0</v>
-      </c>
-      <c r="O19" s="10">
-        <v>0</v>
-      </c>
-      <c r="P19" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="10">
-        <v>0</v>
-      </c>
-      <c r="R19" s="10">
-        <v>0</v>
-      </c>
-      <c r="S19" s="10">
-        <v>0</v>
-      </c>
-      <c r="T19" s="10">
-        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>177</v>
@@ -3122,71 +3156,57 @@
         <v>209</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G20" s="15">
-        <f>2*0.00001</f>
-        <v>2.0000000000000002E-5</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="H20" s="10">
-        <f>0.00001 / 10 / 5 / 10 * 6</f>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" ref="I20:T20" si="8">0.00001 / 10 / 5 / 10 * 6</f>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" si="8"/>
-        <v>1.2000000000000002E-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>177</v>
@@ -3198,7 +3218,7 @@
         <v>209</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>224</v>
@@ -3208,198 +3228,212 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="H21" s="10">
+        <f>0.00001 / 10 / 5 / 10 * 6</f>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="I21" s="10">
+        <f t="shared" ref="I21:T21" si="6">0.00001 / 10 / 5 / 10 * 6</f>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="J21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="O21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="P21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="Q21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="R21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="S21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+      <c r="T21" s="10">
+        <f t="shared" si="6"/>
+        <v>1.2000000000000002E-7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G22" s="15">
+        <f>2*0.00001</f>
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="H22" s="10">
         <f xml:space="preserve"> 0.001</f>
         <v>1E-3</v>
       </c>
-      <c r="I21" s="10">
-        <f t="shared" ref="I21:T21" si="9" xml:space="preserve"> 0.001</f>
+      <c r="I22" s="10">
+        <f t="shared" ref="I22:T22" si="7" xml:space="preserve"> 0.001</f>
         <v>1E-3</v>
       </c>
-      <c r="J21" s="10">
-        <f t="shared" si="9"/>
+      <c r="J22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="K21" s="10">
-        <f t="shared" si="9"/>
+      <c r="K22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="L21" s="10">
-        <f t="shared" si="9"/>
+      <c r="L22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="M21" s="10">
-        <f t="shared" si="9"/>
+      <c r="M22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="N21" s="10">
-        <f t="shared" si="9"/>
+      <c r="N22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="O21" s="10">
-        <f t="shared" si="9"/>
+      <c r="O22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="P21" s="10">
-        <f t="shared" si="9"/>
+      <c r="P22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="Q21" s="10">
-        <f t="shared" si="9"/>
+      <c r="Q22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="R21" s="10">
-        <f t="shared" si="9"/>
+      <c r="R22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="S21" s="10">
-        <f t="shared" si="9"/>
+      <c r="S22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
-      <c r="T21" s="10">
-        <f t="shared" si="9"/>
+      <c r="T22" s="10">
+        <f t="shared" si="7"/>
         <v>1E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E23" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F23" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G23" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H23" s="10">
         <f>0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="I22" s="10">
-        <f t="shared" ref="I22:T22" si="10">0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
+      <c r="I23" s="10">
+        <f t="shared" ref="I23:T23" si="8">0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="J22" s="10">
-        <f t="shared" si="10"/>
+      <c r="J23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="K22" s="10">
-        <f t="shared" si="10"/>
+      <c r="K23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="L22" s="10">
-        <f t="shared" si="10"/>
+      <c r="L23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="M22" s="10">
-        <f t="shared" si="10"/>
+      <c r="M23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="N22" s="10">
-        <f t="shared" si="10"/>
+      <c r="N23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="O22" s="10">
-        <f t="shared" si="10"/>
+      <c r="O23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="P22" s="10">
-        <f t="shared" si="10"/>
+      <c r="P23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="Q22" s="10">
-        <f t="shared" si="10"/>
+      <c r="Q23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="R22" s="10">
-        <f t="shared" si="10"/>
+      <c r="R23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="S22" s="10">
-        <f t="shared" si="10"/>
+      <c r="S23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
       </c>
-      <c r="T22" s="10">
-        <f t="shared" si="10"/>
+      <c r="T23" s="10">
+        <f t="shared" si="8"/>
         <v>1.2000000000000002E-5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="G23" s="16">
-        <v>0.2</v>
-      </c>
-      <c r="H23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="I23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="J23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="K23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="L23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="M23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="N23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="O23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="P23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="R23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="S23" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="T23" s="10">
-        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>177</v>
@@ -3411,57 +3445,57 @@
         <v>254</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="O24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="P24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="R24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="S24" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="T24" s="10" t="s">
-        <v>181</v>
+        <v>192</v>
+      </c>
+      <c r="G24" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="I24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="J24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="M24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="P24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="R24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="S24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="T24" s="10">
+        <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>177</v>
@@ -3473,346 +3507,345 @@
         <v>254</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="R25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="S25" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="T25" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" s="16">
         <f>2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="H25" s="10">
-        <f t="shared" ref="H25:T25" si="11">2*0.1</f>
+      <c r="H26" s="10">
+        <f t="shared" ref="H26:T26" si="9">2*0.1</f>
         <v>0.2</v>
       </c>
-      <c r="I25" s="10">
-        <f t="shared" si="11"/>
+      <c r="I26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="J25" s="10">
-        <f t="shared" si="11"/>
+      <c r="J26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="K25" s="10">
-        <f t="shared" si="11"/>
+      <c r="K26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="L25" s="10">
-        <f t="shared" si="11"/>
+      <c r="L26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="M25" s="10">
-        <f t="shared" si="11"/>
+      <c r="M26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="N25" s="10">
-        <f t="shared" si="11"/>
+      <c r="N26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="O25" s="10">
-        <f t="shared" si="11"/>
+      <c r="O26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="P25" s="10">
-        <f t="shared" si="11"/>
+      <c r="P26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="Q25" s="10">
-        <f t="shared" si="11"/>
+      <c r="Q26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="R25" s="10">
-        <f t="shared" si="11"/>
+      <c r="R26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="S25" s="10">
-        <f t="shared" si="11"/>
+      <c r="S26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="T25" s="10">
-        <f t="shared" si="11"/>
+      <c r="T26" s="10">
+        <f t="shared" si="9"/>
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="G26" s="16">
-        <v>1E-3</v>
-      </c>
-      <c r="H26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="I26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="J26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="K26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="L26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="M26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="N26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="O26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="P26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="Q26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="R26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="S26" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="T26" s="10">
-        <v>1E-3</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>209</v>
+        <v>253</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="H27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="I27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="J27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="K27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="L27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="M27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="N27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="O27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="P27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="R27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="S27" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="T27" s="10">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G28" s="14">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H28" s="10">
         <f>0.00001 / 2 * 10 /2 / 3 / 3 / 3</f>
         <v>9.2592592592592594E-7</v>
       </c>
-      <c r="I27" s="10">
-        <f t="shared" ref="I27:T27" si="12">0.00001 / 2 * 10 /2 / 3 / 3 / 3</f>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="J27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="K27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="L27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="M27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="N27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="O27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="P27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="Q27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="R27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="S27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-      <c r="T27" s="10">
-        <f t="shared" si="12"/>
-        <v>9.2592592592592594E-7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="I28" s="10">
+        <f>0.00001 / 2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" ref="J28:T28" si="10">0.00001 / 2</f>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="O28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="P28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="Q28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="R28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="S28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="T28" s="10">
+        <f t="shared" si="10"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E29" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F29" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G29" s="14">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H29" s="10">
         <f>0.000000005 / 5 *10 / 2 / 3 / 2 / 2</f>
         <v>4.1666666666666668E-10</v>
       </c>
-      <c r="I28" s="10">
-        <f t="shared" ref="I28:T28" si="13">0.000000005 / 5 *10 / 2 / 3 / 2 / 2</f>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="J28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="K28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="L28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="M28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="N28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="O28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="P28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="Q28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="R28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="S28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-      <c r="T28" s="10">
-        <f t="shared" si="13"/>
-        <v>4.1666666666666668E-10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="10">
-        <f t="shared" ref="G29" si="14">0.00002 / 14 / 5</f>
-        <v>2.8571428571428575E-7</v>
-      </c>
-      <c r="H29" s="10">
-        <v>0</v>
-      </c>
       <c r="I29" s="10">
-        <v>0</v>
+        <f>0.000000005 / 5</f>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="J29" s="10">
-        <v>0</v>
+        <f t="shared" ref="J29:T29" si="11">0.000000005 / 5</f>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="K29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="L29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="M29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="N29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="O29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="P29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="Q29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="R29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="S29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>1.0000000000000001E-9</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>177</v>
@@ -3830,8 +3863,8 @@
         <v>232</v>
       </c>
       <c r="G30" s="10">
-        <f t="shared" ref="G30" si="15">0.00002 / 14 / 5 /10</f>
-        <v>2.8571428571428575E-8</v>
+        <f t="shared" ref="G30" si="12">0.00002 / 14 / 5</f>
+        <v>2.8571428571428575E-7</v>
       </c>
       <c r="H30" s="10">
         <v>0</v>
@@ -3874,70 +3907,71 @@
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>276</v>
+      <c r="A31" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>177</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="G31" s="14">
-        <v>260</v>
+        <v>253</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G31" s="10">
+        <f t="shared" ref="G31" si="13">0.00002 / 14 / 5 /10</f>
+        <v>2.8571428571428575E-8</v>
       </c>
       <c r="H31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="I31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="J31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="K31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="M31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="N31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="O31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="P31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="R31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="S31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="T31" s="10">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>282</v>
+      <c r="A32" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>177</v>
@@ -3949,67 +3983,418 @@
         <v>209</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="14">
+        <v>260</v>
+      </c>
+      <c r="H32" s="10">
+        <v>260</v>
+      </c>
+      <c r="I32" s="10">
+        <v>260</v>
+      </c>
+      <c r="J32" s="10">
+        <v>260</v>
+      </c>
+      <c r="K32" s="10">
+        <v>260</v>
+      </c>
+      <c r="L32" s="10">
+        <v>260</v>
+      </c>
+      <c r="M32" s="10">
+        <v>260</v>
+      </c>
+      <c r="N32" s="10">
+        <v>260</v>
+      </c>
+      <c r="O32" s="10">
+        <v>260</v>
+      </c>
+      <c r="P32" s="10">
+        <v>260</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>260</v>
+      </c>
+      <c r="R32" s="10">
+        <v>260</v>
+      </c>
+      <c r="S32" s="10">
+        <v>260</v>
+      </c>
+      <c r="T32" s="10">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G33" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="J32" s="10" t="s">
+      <c r="J33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="K32" s="10" t="s">
+      <c r="K33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="L32" s="10" t="s">
+      <c r="L33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="M32" s="10" t="s">
+      <c r="M33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="N32" s="10" t="s">
+      <c r="N33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="O32" s="10" t="s">
+      <c r="O33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="P32" s="10" t="s">
+      <c r="P33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="Q32" s="10" t="s">
+      <c r="Q33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="R32" s="10" t="s">
+      <c r="R33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="S32" s="10" t="s">
+      <c r="S33" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="T32" s="10" t="s">
+      <c r="T33" s="10" t="s">
         <v>284</v>
       </c>
     </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="G34" s="12">
+        <v>5.9999999999999997E-14</v>
+      </c>
+      <c r="H34" s="10">
+        <f>0.0000000000005* (6 * 12 / 0.44) * 0.0173 / 14 / 1.4 / 10 / 2 * 2</f>
+        <v>7.221706864564007E-15</v>
+      </c>
+      <c r="I34" s="10">
+        <f>0.0000000000005* (6 * 12 / 0.44) * 0.0173 / 14 / 1.4 / 10 / 2 /2</f>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" ref="J34:T34" si="14">0.0000000000005* (6 * 12 / 0.44) * 0.0173 / 14 / 1.4 / 10 / 2/2</f>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="O34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="P34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="Q34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="R34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="S34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+      <c r="T34" s="10">
+        <f t="shared" si="14"/>
+        <v>1.8054267161410017E-15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G35" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="J35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="L35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="N35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="O35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="P35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="R35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="S35" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="T35" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="G36" s="12">
+        <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="H36" s="10">
+        <f>0.00000001</f>
+        <v>1E-8</v>
+      </c>
+      <c r="I36" s="20">
+        <f>0.0000002*100</f>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="J36" s="20">
+        <f t="shared" ref="J36:T36" si="15">0.0000002*100</f>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="K36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="L36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="M36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="N36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="O36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="P36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="Q36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="R36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="S36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+      <c r="T36" s="20">
+        <f t="shared" si="15"/>
+        <v>1.9999999999999998E-5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="G37" s="12">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="H37" s="10">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="I37" s="10">
+        <f>0.01*3</f>
+        <v>0.03</v>
+      </c>
+      <c r="J37" s="10">
+        <f t="shared" ref="J37:T37" si="16">0.01*3</f>
+        <v>0.03</v>
+      </c>
+      <c r="K37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="L37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="M37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="O37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="P37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="Q37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="R37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="S37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+      <c r="T37" s="10">
+        <f t="shared" si="16"/>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H40" s="21"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="G29:G30">
-    <cfRule type="colorScale" priority="629">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="628">
+  <conditionalFormatting sqref="G14">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4020,18 +4405,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G30:T30">
-    <cfRule type="colorScale" priority="730">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="731">
+  <conditionalFormatting sqref="G30:G31">
+    <cfRule type="colorScale" priority="654">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="655">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4042,18 +4427,84 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16:H17">
-    <cfRule type="colorScale" priority="128">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="127">
+  <conditionalFormatting sqref="G31:T31">
+    <cfRule type="colorScale" priority="756">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="757">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="colorScale" priority="153">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="154">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H36">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4065,17 +4516,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:T6">
-    <cfRule type="colorScale" priority="733">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="734">
+    <cfRule type="colorScale" priority="759">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="760">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4087,17 +4538,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:T7">
-    <cfRule type="colorScale" priority="735">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="736">
+    <cfRule type="colorScale" priority="761">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="762">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4109,17 +4560,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:T8">
-    <cfRule type="colorScale" priority="737">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="738">
+    <cfRule type="colorScale" priority="763">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="764">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4131,17 +4582,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:T9">
-    <cfRule type="colorScale" priority="739">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="740">
+    <cfRule type="colorScale" priority="765">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="766">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4153,17 +4604,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:T10">
-    <cfRule type="colorScale" priority="741">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="742">
+    <cfRule type="colorScale" priority="767">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="768">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4175,17 +4626,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:T11">
-    <cfRule type="colorScale" priority="744">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="743">
+    <cfRule type="colorScale" priority="769">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="770">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4197,17 +4648,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:T13">
-    <cfRule type="colorScale" priority="746">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="745">
+    <cfRule type="colorScale" priority="771">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="772">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4219,17 +4670,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:T14">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="36">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4241,17 +4692,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:T15">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="30">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4262,18 +4713,40 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18:T18">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="H16:T16">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:T17">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4285,17 +4758,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:T19">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4307,17 +4780,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H20:T20">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4329,17 +4802,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H21:T21">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4351,17 +4824,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H22:T22">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4372,18 +4845,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H23:T26">
-    <cfRule type="colorScale" priority="753">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="754">
+  <conditionalFormatting sqref="H23:T23">
+    <cfRule type="colorScale" priority="39">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4394,18 +4867,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H27:T27">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="H24:T27">
+    <cfRule type="colorScale" priority="779">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="780">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4417,17 +4890,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:T28">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4438,18 +4911,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H29:T30">
-    <cfRule type="colorScale" priority="728">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="729">
+  <conditionalFormatting sqref="H29:T29">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4460,38 +4933,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31:T31">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="H30:T31">
+    <cfRule type="colorScale" priority="754">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="755">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4503,37 +4956,123 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H32:T32">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H33:T33">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H34:T34">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H35:T35">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4545,17 +5084,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="colorScale" priority="156">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="155">
+    <cfRule type="colorScale" priority="181">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="182">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4566,18 +5105,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16:T16">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="27">
+  <conditionalFormatting sqref="I18:T18">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4588,18 +5127,30 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I17:T17">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="25">
+  <conditionalFormatting sqref="I36:T36">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I37:T37">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4611,17 +5162,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3">
-    <cfRule type="colorScale" priority="153">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="154">
+    <cfRule type="colorScale" priority="179">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4633,17 +5184,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="colorScale" priority="151">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="152">
+    <cfRule type="colorScale" priority="177">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="178">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4655,17 +5206,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3">
-    <cfRule type="colorScale" priority="150">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="149">
+    <cfRule type="colorScale" priority="175">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4677,17 +5228,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3">
-    <cfRule type="colorScale" priority="147">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="148">
+    <cfRule type="colorScale" priority="173">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4699,17 +5250,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3">
-    <cfRule type="colorScale" priority="145">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="146">
+    <cfRule type="colorScale" priority="171">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="172">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4721,17 +5272,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3">
-    <cfRule type="colorScale" priority="143">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="144">
+    <cfRule type="colorScale" priority="169">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4743,17 +5294,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="colorScale" priority="141">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="142">
+    <cfRule type="colorScale" priority="167">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4765,17 +5316,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3">
-    <cfRule type="colorScale" priority="140">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="139">
+    <cfRule type="colorScale" priority="165">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4787,17 +5338,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R3">
-    <cfRule type="colorScale" priority="138">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="137">
+    <cfRule type="colorScale" priority="163">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4809,17 +5360,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="colorScale" priority="135">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="136">
+    <cfRule type="colorScale" priority="161">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4831,17 +5382,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T3">
-    <cfRule type="colorScale" priority="131">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="132">
+    <cfRule type="colorScale" priority="157">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="158">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4860,7 +5411,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C169"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="35.7109375" customWidth="1"/>
     <col min="3" max="3" width="49.5703125" customWidth="1"/>

--- a/simulations/scene/inputs/Scenarios_25_12_11.xlsx
+++ b/simulations/scene/inputs/Scenarios_25_12_11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TIGERA~1\AppData\Local\Temp\scp54510\work_home\tigerault\Wheat-BRIDGES_framework\Root-CyNAPS\simulations\scene\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1762FF8-D615-4F88-A1F7-2E488AC900AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD979268-BC1C-4272-97D7-F893FA96465F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios_as_columns" sheetId="2" r:id="rId1"/>
@@ -4191,43 +4191,43 @@
         <v>0.1</v>
       </c>
       <c r="H35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="J35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="K35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="M35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="N35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="O35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="P35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="Q35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="R35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="S35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="T35" s="10">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -4560,17 +4560,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8:T8">
+    <cfRule type="colorScale" priority="764">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="763">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="764">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4582,17 +4582,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:T9">
+    <cfRule type="colorScale" priority="766">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="765">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="766">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4648,17 +4648,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13:T13">
+    <cfRule type="colorScale" priority="772">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="771">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="772">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4670,17 +4670,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:T14">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4692,17 +4692,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:T15">
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4758,17 +4758,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19:T19">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4868,17 +4868,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24:T27">
+    <cfRule type="colorScale" priority="780">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="779">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="780">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4890,17 +4890,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28:T28">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4934,17 +4934,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:T31">
+    <cfRule type="colorScale" priority="755">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="754">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="755">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4966,6 +4966,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
@@ -4977,16 +4987,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5040,17 +5040,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H34:T34">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5084,17 +5084,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="182">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="181">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="182">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5162,17 +5162,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3">
+    <cfRule type="colorScale" priority="180">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="179">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5184,17 +5184,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
+    <cfRule type="colorScale" priority="178">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="177">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="178">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5206,17 +5206,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3">
+    <cfRule type="colorScale" priority="176">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="175">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5228,17 +5228,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3">
+    <cfRule type="colorScale" priority="174">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="173">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5250,17 +5250,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3">
+    <cfRule type="colorScale" priority="172">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="171">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="172">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5272,17 +5272,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3">
+    <cfRule type="colorScale" priority="170">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="169">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5316,17 +5316,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3">
+    <cfRule type="colorScale" priority="166">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="165">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5382,17 +5382,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T3">
+    <cfRule type="colorScale" priority="158">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="157">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="158">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
